--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -824,99 +860,99 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - OFERTA ESPECIAL 22/10/25</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>289794</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="n">
-        <v>22.99</v>
+      <c r="C16" s="8" t="n">
+        <v>119927</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - OFERTA ESPECIAL 22/10/25</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>104601</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
-        <v>16.99</v>
+      <c r="C17" s="8" t="n">
+        <v>225767</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>FRANGO BONASA KG CONGELADO</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="10" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 22/10/25</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>105460</v>
+        <v>289794</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA DA PALETA KG</t>
+          <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="6" t="n">
-        <v>23.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 22/10/25</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>105456</v>
+        <v>104601</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>CARNE DE SOL KG SEGUNDA</t>
+          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="6" t="n">
-        <v>28.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="20">
@@ -931,16 +967,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>105468</v>
+        <v>105460</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>CARNE MOIDA KG</t>
+          <t>BISTECA BOVINA DA PALETA KG</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="6" t="n">
-        <v>17.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="21">
@@ -955,16 +991,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>105435</v>
+        <v>105456</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>COXÃO MOLE KG</t>
+          <t>CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="6" t="n">
-        <v>36.99</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="22">
@@ -979,16 +1015,16 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>105474</v>
+        <v>105468</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>FRALDINHA BOVINA KG</t>
+          <t>CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="6" t="n">
-        <v>30.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="23">
@@ -1003,16 +1039,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>107260</v>
+        <v>105435</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t>COXÃO MOLE KG</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="6" t="n">
-        <v>30.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="24">
@@ -1023,20 +1059,20 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>106053</v>
+        <v>105474</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>BISTECA SUINA CARRE KG</t>
+          <t>FRALDINHA BOVINA KG</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="6" t="n">
-        <v>17.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="25">
@@ -1047,20 +1083,20 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>105062</v>
+        <v>107260</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="6" t="n">
-        <v>17.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="26">
@@ -1075,16 +1111,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>106052</v>
+        <v>106053</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>PELE SUINA KG</t>
+          <t>BISTECA SUINA CARRE KG</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="6" t="n">
-        <v>11.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="27">
@@ -1099,88 +1135,88 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>106050</v>
+        <v>105062</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>PÉ SUINO KG</t>
+          <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="6" t="n">
-        <v>9.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
+          <t>QUARTA - AÇOUGUE 22/10/25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #04 PEIXES</t>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>203713</v>
+        <v>106052</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>FILÉ DE TILAPIA BOUA 800G</t>
+          <t>PELE SUINA KG</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="6" t="n">
-        <v>41.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
+          <t>QUARTA - AÇOUGUE 22/10/25</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>194424</v>
+        <v>106050</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA CALABRESA BOUA 400G</t>
+          <t>PÉ SUINO KG</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="6" t="n">
-        <v>13.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 22/10/25</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #04 PEIXES</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>305039</v>
+        <v>203713</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA CASEIRA BOVINA KG</t>
+          <t>FILÉ DE TILAPIA BOUA 800G</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="6" t="n">
-        <v>17.99</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="31">
@@ -1195,22 +1231,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>289127</v>
+        <v>194424</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
+          <t>LINGUIÇA CALABRESA BOUA 400G</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="n">
-        <v>7.89</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
+          <t>QUARTA - AÇOUGUE 22/10/25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1219,16 +1255,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>105765</v>
+        <v>305039</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORTADELA PERDIGAO KG MISTA </t>
+          <t>LINGUIÇA CASEIRA BOVINA KG</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="n">
-        <v>9.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="33">
@@ -1243,16 +1279,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>105770</v>
+        <v>289127</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
+          <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="n">
-        <v>11.7</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="34">
@@ -1267,16 +1303,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>252392</v>
+        <v>105765</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>PEITO DE PERU SADIA 200G DEFUMADO FATIAS FINAS</t>
+          <t xml:space="preserve">MORTADELA PERDIGAO KG MISTA </t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="n">
-        <v>15.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="35">
@@ -1291,144 +1327,144 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>173481</v>
+        <v>105770</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>SALAME ITALIANO SEARA 100G FATIADO</t>
+          <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="6" t="n">
-        <v>10.99</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>252392</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>PEITO DE PERU SADIA 200G DEFUMADO FATIAS FINAS</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="6" t="n">
+        <v>15.99</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>104931</v>
+        <v>173481</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>SALAME ITALIANO SEARA 100G FATIADO</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="6" t="n">
-        <v>7.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>QUARTA - HORTIFRUTI 22/10/25</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C39" s="8" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="10" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
         <v>104928</v>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>MANGA KG PALMER</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="6" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="10" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>QUARTA - HORTIFRUTI 22/10/25</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C41" s="8" t="n">
         <v>104883</v>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>MANGA KG TOMY</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="6" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 22/10/25</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>104944</v>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>MAÇÃ NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="6" t="n">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 22/10/25</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>104947</v>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="6" t="n">
-        <v>2.39</v>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="10" t="n">
+        <v>6.99</v>
       </c>
     </row>
     <row r="42">
@@ -1443,184 +1479,256 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>104996</v>
+        <v>104944</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>MELÃO AMARELO KG</t>
+          <t>MAÇÃ NACIONAL KG</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="6" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>104947</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="10" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>104996</v>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>MELÃO AMARELO KG</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="10" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>105010</v>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="10" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>105001</v>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="10" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>104862</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr"/>
+      <c r="F47" s="10" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>104961</v>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr"/>
+      <c r="F48" s="10" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 22/10/25</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>104863</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>TOMATE SALADETE KG</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr"/>
+      <c r="F49" s="10" t="n">
         <v>6.99</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>QUARTA - HORTIFRUTI 22/10/25</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>105010</v>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>104937</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>ALHO A GRANEL KG</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="6" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>QUARTA - HORTIFRUTI 22/10/25</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>105001</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>104919</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>CEBOLA NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr"/>
+      <c r="F51" s="10" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>QUARTA - HORTIFRUTI 22/10/25</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>104862</v>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 22/10/25</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>104961</v>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>TOMATE CARMEM KG</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 22/10/25</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>104937</v>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>ALHO A GRANEL KG</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="n">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 22/10/25</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>104919</v>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>CEBOLA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="6" t="n">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 22/10/25</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C52" s="8" t="n">
         <v>104992</v>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="6" t="n">
-        <v>3.99</v>
+      <c r="E52" s="9" t="inlineStr"/>
+      <c r="F52" s="10" t="n">
+        <v>3.39</v>
       </c>
     </row>
   </sheetData>

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,24 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -59,7 +77,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,24 +115,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -522,894 +558,866 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
+          <t>REVEILLON GIRO PRAÇA - OFERTA ESPECIAL</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+          <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>247972</v>
+        <v>100038</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>BEBIDA ICE 51 275ML</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>AÇAI COM GUARANA, BALADA, KIWI, LIMÃO, MARACUJA, MAÇÃ VERDE, MORANGO COM LARANJA, TANGERINA, ZERO 3 LIMÕES</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>6.49</v>
+          <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>21.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
+          <t>REVEILLON GIRO PRAÇA - OFERTA ESPECIAL</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+          <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>247970</v>
+        <v>100031</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>BEBIDA ICE 51 6 X 275ML</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BALADA, KIWI, LIMÃO, MARACUJA, MORANGO COM LARANJA, TANGERINA</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>6.49</v>
+          <t>ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="5" t="n">
+        <v>21.99</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>117100</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ENERGETICO EXTRA POWER 2L</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="n">
-        <v>13.99</v>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>REVEILLON GIRO PRAÇA - OFERTA ESPECIAL</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>297920</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CHOCOLATE EM BARRA NEUGEBAUER 80G</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>AMENDOIN, AO LEITE, BRANCO, CARAMELO, COOKIES, FLOCOS, MEIO AMA, PRETO BRANCO</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>247972</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>BEBIDA ICE 51 275ML</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>AÇAI COM GUARANA, BALADA, KIWI, LIMÃO, MARACUJA, MAÇÃ VERDE, MORANGO COM LARANJA, TANGERINA, ZERO 3 LIMÕES</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>247970</v>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>BEBIDA ICE 51 6 X 275ML</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>BALADA, KIWI, LIMÃO, MARACUJA, MORANGO COM LARANJA, TANGERINA</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>117100</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>ENERGETICO EXTRA POWER 2L</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="10" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C10" s="7" t="n">
         <v>314219</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA ORIGINAL LONG NECK 300ML</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="n">
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="10" t="n">
         <v>4.39</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C11" s="7" t="n">
         <v>247800</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>CERVEJA BUDWEISER LAGER LONG NECK 330ML</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="10" t="n">
         <v>6.19</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C12" s="7" t="n">
         <v>171723</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>CERVEJA CORONITA LONG NECK 210ML</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="n">
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="10" t="n">
         <v>7.19</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C13" s="7" t="n">
         <v>287369</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA ANTARCTICA ORIGINAL 15 X 269ML </t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="6" t="n">
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="10" t="n">
         <v>3.99</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C14" s="7" t="n">
         <v>193099</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA ANTARCTICA ORIGINAL LONG NECK 12 X 300ML </t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="n">
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="n">
         <v>4.39</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C15" s="7" t="n">
         <v>215568</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>CACHAÇA BANANAZINHA 900ML</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="6" t="n">
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="10" t="n">
         <v>36.99</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C16" s="7" t="n">
         <v>301843</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>CAMPARI 998ML</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="n">
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
         <v>78.98999999999999</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C17" s="7" t="n">
         <v>284865</v>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>CONHAQUE DREHER 900ML ORIGINAL</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="6" t="n">
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="10" t="n">
         <v>29.99</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C18" s="7" t="n">
         <v>117358</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>TEQUILA JOSE CUERVO 750ML ESPECIAL</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="n">
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="10" t="n">
         <v>189.99</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C19" s="7" t="n">
         <v>102087</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>VODKA SMIRNOFF 998ML TRIPLE DISTILLED</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="n">
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="10" t="n">
         <v>49.99</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C20" s="7" t="n">
         <v>110367</v>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>WHISKY JACK DANIELS 1L</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="n">
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="10" t="n">
         <v>199.99</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C21" s="7" t="n">
         <v>193190</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>WHISKY JOHNNIE WALKER 750ML RED LABEL</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="n">
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="10" t="n">
         <v>89.98999999999999</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C22" s="7" t="n">
         <v>102077</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>WHISKY OLD PARR 1L 12 ANOS</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="10" t="n">
         <v>185.99</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C23" s="7" t="n">
         <v>297481</v>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>CHOPP DE VINHO STEMPEL 600ML</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>PINEAPPLE, PINK, RED, WHITE</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F23" s="10" t="n">
         <v>11.99</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C24" s="7" t="n">
         <v>131178</v>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>ESPUMANTE CERESER CELEBRATE 660ML</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="n">
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="10" t="n">
         <v>11.99</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA - 31/12/25</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C25" s="7" t="n">
         <v>101958</v>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>ESPUMANTE CERESER SIDRA 660ML CLASSIC</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="n">
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="10" t="n">
         <v>15.99</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C27" s="7" t="n">
         <v>105450</v>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>ALCATRA BOVINA KG</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="n">
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="10" t="n">
         <v>38.99</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C28" s="7" t="n">
         <v>105461</v>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="n">
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="10" t="n">
         <v>33.99</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C29" s="7" t="n">
         <v>105468</v>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>CARNE MOIDA KG</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="6" t="n">
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C30" s="7" t="n">
         <v>105458</v>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>CHAMBARI KG</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="n">
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C31" s="7" t="n">
         <v>105471</v>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>COSTELA BOVINA KG</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="n">
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="10" t="n">
         <v>17.99</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C32" s="7" t="n">
         <v>105474</v>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>FRALDINHA BOVINA KG</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="n">
+      <c r="E32" s="9" t="inlineStr"/>
+      <c r="F32" s="10" t="n">
         <v>32.99</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C33" s="7" t="n">
         <v>107260</v>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="n">
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="10" t="n">
         <v>29.99</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C34" s="7" t="n">
         <v>106053</v>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>BISTECA SUINA CARRE KG</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="n">
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C35" s="7" t="n">
         <v>105062</v>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="n">
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C36" s="7" t="n">
         <v>105433</v>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>COSTELA SUINA KG</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="6" t="n">
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="10" t="n">
         <v>24.99</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C37" s="7" t="n">
         <v>258810</v>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>PANCETA SUINA KG</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="6" t="n">
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="10" t="n">
         <v>16.99</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO DA PRAÇA- AÇOUGUE 31/12/25</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C38" s="7" t="n">
         <v>305039</v>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>LINGUIÇA CASEIRA BOVINA KG</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="6" t="n">
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>105023</v>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="6" t="n">
-        <v>6.49</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>104931</v>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>LARANJA KG</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="6" t="n">
-        <v>6.89</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>104928</v>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG PALMER</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="6" t="n">
-        <v>7.39</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>104883</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG TOMY</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="6" t="n">
-        <v>7.39</v>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>104944</v>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>MAÇÃ NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="6" t="n">
-        <v>13.99</v>
-      </c>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1423,208 +1431,208 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
+        <v>104864</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>ABACATE KG</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="5" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>105023</v>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>BANANA PRATA KG</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="10" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="10" t="n">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>104928</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>MANGA KG PALMER</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="10" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>104883</v>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>MANGA KG TOMY</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="10" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>104944</v>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>MAÇÃ NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="10" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
         <v>104947</v>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="6" t="n">
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="10" t="n">
         <v>2.49</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C47" s="7" t="n">
         <v>104996</v>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>MELÃO AMARELO KG</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="6" t="n">
+      <c r="E47" s="9" t="inlineStr"/>
+      <c r="F47" s="10" t="n">
         <v>7.39</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C48" s="7" t="n">
         <v>104903</v>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>BATATA DOCE KG ROSA</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="6" t="n">
+      <c r="E48" s="9" t="inlineStr"/>
+      <c r="F48" s="10" t="n">
         <v>6.39</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>105010</v>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="6" t="n">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>105001</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>104862</v>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="6" t="n">
-        <v>6.39</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>104961</v>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>TOMATE CARMEM KG</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>104937</v>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>ALHO A GRANEL KG</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="n">
-        <v>22.99</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>104919</v>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>CEBOLA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="6" t="n">
-        <v>3.49</v>
       </c>
     </row>
     <row r="49">
@@ -1635,52 +1643,68 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>104992</v>
+        <v>105010</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="6" t="n">
-        <v>3.99</v>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="5" t="n">
+        <v>5.99</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>105001</v>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr"/>
+      <c r="F50" s="10" t="n">
+        <v>5.99</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>#10 OVOS</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>331438</v>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 20UN BRANCOS </t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="6" t="n">
-        <v>11.99</v>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>104862</v>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr"/>
+      <c r="F51" s="10" t="n">
+        <v>6.39</v>
       </c>
     </row>
     <row r="52">
@@ -1691,19 +1715,147 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>104961</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="5" t="n">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>104937</v>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>ALHO A GRANEL KG</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="10" t="n">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>104919</v>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>CEBOLA NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr"/>
+      <c r="F54" s="10" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>104992</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="5" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
           <t>#10 OVOS</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C57" s="7" t="n">
+        <v>331438</v>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 20UN BRANCOS </t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr"/>
+      <c r="F57" s="10" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>REVEILLON GIRO PRAÇA - HORTI 31/12/25</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>#10 OVOS</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
         <v>328966</v>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="n">
+      <c r="E58" s="9" t="inlineStr"/>
+      <c r="F58" s="10" t="n">
         <v>17.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,24 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -59,7 +77,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,24 +115,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,13 +512,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -522,98 +558,82 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>157014</v>
+        <v>100038</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="6" t="n">
-        <v>13.99</v>
+          <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>21.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>105470</v>
+        <v>100020</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>ACEM BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="6" t="n">
-        <v>23.99</v>
+          <t>ARROZ REALENGO PCT 5KG TIPO 1 BRANCO</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="5" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>239334</v>
+        <v>100031</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>CAPA DO CONTRA FILE KG</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="n">
-        <v>28.99</v>
+          <t>ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="5" t="n">
+        <v>21.99</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>105457</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CARNE BOVINA SERENADA KG</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="n">
-        <v>34.99</v>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -623,292 +643,292 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>105853</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>FRANGO MARINGA KG CONGELADO</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C7" s="7" t="n">
+        <v>157014</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO COM OSSO KG</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="10" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>105470</v>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="10" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>239334</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>CAPA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="10" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>105457</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>CARNE BOVINA SERENADA KG</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="10" t="n">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>105458</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>CHAMBARI KG</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C12" s="7" t="n">
         <v>105449</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>COXÃO DURO KG</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="n">
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="10" t="n">
         <v>34.99</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C13" s="7" t="n">
         <v>105435</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>COXÃO MOLE KG</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="6" t="n">
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="10" t="n">
         <v>38.99</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C14" s="7" t="n">
         <v>105062</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="n">
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="n">
         <v>19.99</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C15" s="7" t="n">
         <v>106050</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PÉ SUINO KG</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="6" t="n">
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="10" t="n">
         <v>9.99</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C16" s="7" t="n">
         <v>305039</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>LINGUIÇA CASEIRA BOVINA KG</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="n">
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C18" s="7" t="n">
         <v>105023</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>BANANA PRATA KG</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="n">
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="10" t="n">
         <v>5.99</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>104931</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>LARANJA KG</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="n">
-        <v>8.59</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>104928</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG PALMER</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>104883</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG TOMY</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>104944</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>MAÇÃ NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>104947</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="6" t="n">
-        <v>2.69</v>
       </c>
     </row>
     <row r="19">
@@ -923,160 +943,160 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="5" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>104928</v>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>MANGA KG PALMER</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="10" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>104883</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>MANGA KG TOMY</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="10" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>104944</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>MAÇÃ NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="10" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>104947</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="10" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
         <v>104996</v>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>MELÃO AMARELO KG</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="n">
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="10" t="n">
         <v>7.99</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C25" s="7" t="n">
         <v>104903</v>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>BATATA DOCE KG ROSA</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="n">
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="10" t="n">
         <v>5.99</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>105010</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>105001</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="n">
-        <v>6.49</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>104862</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>104961</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>TOMATE CARMEM KG</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="6" t="n">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>104937</v>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>ALHO A GRANEL KG</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="n">
-        <v>24.99</v>
       </c>
     </row>
     <row r="26">
@@ -1087,20 +1107,20 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>104919</v>
+        <v>105010</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="n">
-        <v>3.99</v>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>4.39</v>
       </c>
     </row>
     <row r="27">
@@ -1111,29 +1131,45 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>104992</v>
+        <v>105001</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="n">
-        <v>4.19</v>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="5" t="n">
+        <v>4.69</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>104862</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>4.89</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1143,19 +1179,123 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>104961</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="5" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>104937</v>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>ALHO A GRANEL KG</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="10" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>104919</v>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>CEBOLA NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="10" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>104992</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="5" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>#10 OVOS</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C34" s="7" t="n">
         <v>328966</v>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="n">
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="10" t="n">
         <v>15.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,24 +35,6 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -77,7 +59,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -88,12 +70,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0045A045"/>
-        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,36 +91,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -512,13 +476,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="57" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -574,8 +538,8 @@
           <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="5" t="n">
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="6" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -598,8 +562,8 @@
           <t>ARROZ REALENGO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="5" t="n">
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="6" t="n">
         <v>19.99</v>
       </c>
     </row>
@@ -622,8 +586,8 @@
           <t>ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="6" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -638,664 +602,1008 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>268844</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>MARGARINA DELICIA 500G COM CREME DE LEITE</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>246975</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>IOGURTE DANONE 1250G MORANGO</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>155246</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>REQUEIJÃO CANTO DE MINAS 200G CREMOSO TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="6" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>111324</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>COXA COM SOBRECOXA SADIA 1KG</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>104602</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>COXA DE FRANGO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>108856</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>108786</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>FILEZINHO DE PEITO DE FRANGO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="6" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>109388</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>FRANGO A PASSARINHO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C15" s="3" t="n">
         <v>105853</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>FRANGO MARINGA KG CONGELADO</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="5" t="n">
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="n">
         <v>10.99</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>157014</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="10" t="n">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>105470</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>ACEM BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="10" t="n">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>108788</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>FRANGO SADIA PCT 1KG CONGELADO A PASSARINHO TEMPERADO</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>108783</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>MEIO DA ASA DE FRANGO SADIA BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>108774</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>MEIO DE DA ASA FRANGO SADIA PCT 1KG TULIPA</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="n">
         <v>23.99</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>239334</v>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>CAPA DO CONTRA FILE KG</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="10" t="n">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>105457</v>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>CARNE BOVINA SERENADA KG</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="10" t="n">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>105458</v>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>CHAMBARI KG</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="10" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>105449</v>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>COXÃO DURO KG</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="10" t="n">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>105435</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>COXÃO MOLE KG</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="10" t="n">
-        <v>38.99</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>105062</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="10" t="n">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>106050</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>PÉ SUINO KG</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="10" t="n">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>305039</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>LINGUIÇA CASEIRA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="10" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>105023</v>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="10" t="n">
-        <v>5.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>104931</v>
+        <v>104601</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="5" t="n">
-        <v>7.99</v>
+          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="6" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>104928</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>MANGA KG PALMER</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="10" t="n">
-        <v>7.99</v>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>157014</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO COM OSSO KG</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="n">
+        <v>13.99</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>104883</v>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>MANGA KG TOMY</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="10" t="n">
-        <v>7.99</v>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>105470</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="n">
+        <v>23.99</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>104944</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>MAÇÃ NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="10" t="n">
-        <v>13.99</v>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>239334</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>CAPA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="6" t="n">
+        <v>28.99</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>104947</v>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="10" t="n">
-        <v>2.69</v>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>105457</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>CARNE BOVINA SERENADA KG</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="n">
+        <v>34.99</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>104996</v>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>MELÃO AMARELO KG</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="10" t="n">
-        <v>7.99</v>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>105458</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="n">
+        <v>18.99</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>104903</v>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>BATATA DOCE KG ROSA</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="10" t="n">
-        <v>5.99</v>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>105449</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>COXÃO DURO KG</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="6" t="n">
+        <v>34.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>105010</v>
+        <v>105435</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="5" t="n">
-        <v>4.39</v>
+          <t>COXÃO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>38.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>105001</v>
+        <v>105062</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="5" t="n">
-        <v>4.69</v>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="6" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>104862</v>
+        <v>106050</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="5" t="n">
-        <v>4.89</v>
+          <t>PÉ SUINO KG</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="6" t="n">
+        <v>9.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+          <t>QUARTA - AÇOUGUE 14/01/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA CASEIRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>189031</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA MISTA FRICÓ KG</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="6" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 14 E 15/01/26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>123758</v>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA TOSCANA MISTA FRIMESA KG</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>105023</v>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>BANANA PRATA KG</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="6" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="6" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>104928</v>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>MANGA KG PALMER</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="6" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>104883</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>MANGA KG TOMY</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="6" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>104944</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>MAÇÃ NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>104947</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="6" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>104996</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>MELÃO AMARELO KG</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="6" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C40" s="3" t="n">
+        <v>104903</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>BATATA DOCE KG ROSA</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="6" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>105010</v>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="6" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>105001</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="6" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>104862</v>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="6" t="n">
+        <v>4.89</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>104961</v>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>TOMATE CARMEM KG</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="5" t="n">
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="6" t="n">
         <v>6.99</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C45" s="3" t="n">
         <v>104937</v>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>ALHO A GRANEL KG</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="10" t="n">
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="6" t="n">
         <v>24.99</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C46" s="3" t="n">
         <v>104919</v>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="10" t="n">
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="6" t="n">
         <v>3.99</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C47" s="3" t="n">
         <v>104992</v>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="5" t="n">
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="6" t="n">
         <v>2.99</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI 14/01/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>#10 OVOS</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C49" s="3" t="n">
         <v>328966</v>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="10" t="n">
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="6" t="n">
         <v>15.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,27 +1124,27 @@
       <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>QUARTA - HORTIFURTI 21/01/26</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>105023</v>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="n">
-        <v>5.99</v>
+      <c r="C27" s="8" t="n">
+        <v>104905</v>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>BANANA NANICA KG</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="10" t="n">
+        <v>4.99</v>
       </c>
     </row>
     <row r="28">
@@ -1123,40 +1159,40 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>104931</v>
+        <v>105023</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="6" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>QUARTA - HORTIFURTI 21/01/26</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
-        <v>104928</v>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG PALMER</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="n">
-        <v>7.99</v>
+      <c r="C29" s="8" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="10" t="n">
+        <v>6.99</v>
       </c>
     </row>
     <row r="30">
@@ -1171,11 +1207,11 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>104883</v>
+        <v>104928</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>MANGA KG TOMY</t>
+          <t>MANGA KG PALMER</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
@@ -1195,16 +1231,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>104944</v>
+        <v>104883</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>MAÇÃ NACIONAL KG</t>
+          <t>MANGA KG TOMY</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="n">
-        <v>13.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="32">
@@ -1219,16 +1255,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>104947</v>
+        <v>104944</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>MAÇÃ NACIONAL KG</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="n">
-        <v>2.69</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="33">
@@ -1243,16 +1279,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>104996</v>
+        <v>104947</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>MELÃO AMARELO KG</t>
+          <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="34">
@@ -1263,20 +1299,20 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>104903</v>
+        <v>104996</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>BATATA DOCE KG ROSA</t>
+          <t>MELÃO AMARELO KG</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="35">
@@ -1352,27 +1388,27 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>QUARTA - HORTIFURTI 21/01/26</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="8" t="n">
         <v>104961</v>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>TOMATE CARMEM KG</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="6" t="n">
-        <v>6.99</v>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="10" t="n">
+        <v>7.99</v>
       </c>
     </row>
     <row r="39">

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,24 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -59,7 +77,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,24 +115,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,13 +512,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -522,633 +558,617 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>157014</v>
+        <v>276943</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="6" t="n">
-        <v>12.99</v>
+          <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>16.19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>105470</v>
+        <v>306946</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>ACEM BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="6" t="n">
-        <v>23.99</v>
+          <t>BEBIDA LACTEA FRUTILAC BDJ 480G MORANGO</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="5" t="n">
+        <v>4.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>105450</v>
+        <v>246975</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>ALCATRA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="n">
-        <v>38.99</v>
+          <t>IOGURTE DANONE 1250G MORANGO</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="5" t="n">
+        <v>21.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>105461</v>
+        <v>101874</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA DO CONTRA FILE KG</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="n">
-        <v>33.99</v>
+          <t>TODDYNHO 200ML CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>105456</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>CARNE DE SOL KG SEGUNDA</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
-        <v>28.99</v>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>105451</v>
+        <v>111324</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>CONTRA FILÉ KG</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="n">
-        <v>38.99</v>
+          <t>COXA COM SOBRECOXA SADIA 1KG</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="5" t="n">
+        <v>20.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>105463</v>
+        <v>104602</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>CORAÇÃO BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="6" t="n">
+          <t>COXA DE FRANGO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
         <v>13.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>105471</v>
+        <v>108785</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="n">
-        <v>19.99</v>
+          <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="5" t="n">
+        <v>18.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>105062</v>
+        <v>108786</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="6" t="n">
-        <v>18.99</v>
+          <t>FILEZINHO DE PEITO DE FRANGO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>24.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>106052</v>
+        <v>108774</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>PELE SUINA KG</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="n">
-        <v>12.99</v>
+          <t>MEIO DE DA ASA FRANGO SADIA PCT 1KG TULIPA</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="5" t="n">
+        <v>23.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>104601</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>QUARTA - AÇOUGUE 28/01/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>157014</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO COM OSSO KG</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="10" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>105470</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>105450</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>ALCATRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="10" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>105461</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>BISTECA BOVINA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>105456</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>CARNE DE SOL KG SEGUNDA</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="10" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>105451</v>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>CONTRA FILÉ KG</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="10" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>105463</v>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CORAÇÃO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="10" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>COSTELA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="10" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C21" s="7" t="n">
+        <v>105062</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="10" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>106052</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>PELE SUINA KG</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="10" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 28/01/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
         <v>106032</v>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>TOUCINHO FRESCO KG</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="6" t="n">
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="10" t="n">
         <v>18.99</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>104864</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>ABACATE KG</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>104905</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>BANANA NANICA KG</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>105023</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>104931</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>LARANJA KG</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>104855</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>LIMÃO TAITI KG</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="6" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>104928</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG PALMER</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>104883</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG TOMY</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>104944</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>MAÇÃ NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="6" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>104947</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>104996</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>MELÃO AMARELO KG</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="n">
-        <v>6.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTI 28/01/26</t>
+          <t>QUARTA/QUINTA - 28 E 29/01/26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>104903</v>
+        <v>301962</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>BATATA DOCE KG ROSA</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="6" t="n">
-        <v>6.99</v>
+          <t>LINGUIÇA SUÍNA BONFRIGO KG</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>17.99</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>105010</v>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="n">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>104864</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>ABACATE KG</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="10" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>104905</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>BANANA NANICA KG</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="10" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>105023</v>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>BANANA PRATA KG</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="10" t="n">
         <v>5.99</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>105001</v>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>104862</v>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>104961</v>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>TOMATE CARMEM KG</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="n">
-        <v>6.99</v>
       </c>
     </row>
     <row r="29">
@@ -1159,99 +1179,411 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="5" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>104855</v>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>LIMÃO TAITI KG</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="10" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>104928</v>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>MANGA KG PALMER</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="10" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>104883</v>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>MANGA KG TOMY</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr"/>
+      <c r="F32" s="10" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>104944</v>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>MAÇÃ NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="10" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>104947</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="5" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>104996</v>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>MELÃO AMARELO KG</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="10" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>104903</v>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>BATATA DOCE KG ROSA</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="10" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>105010</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="5" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>105001</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="5" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>104862</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>104961</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="5" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C41" s="7" t="n">
         <v>104937</v>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>ALHO A GRANEL KG</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="n">
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="10" t="n">
         <v>24.99</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C42" s="7" t="n">
         <v>104919</v>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="n">
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="10" t="n">
         <v>3.99</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C43" s="7" t="n">
         <v>104992</v>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="6" t="n">
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="10" t="n">
         <v>2.99</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTI 28/01/26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>#10 OVOS</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C45" s="3" t="n">
+        <v>239922</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>OVOS DE GRANJA BDJ 12UN BRANCOS</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="5" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTI 28/01/26</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>#10 OVOS</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
         <v>328966</v>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="6" t="n">
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -796,348 +832,348 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 04 E 05/02/26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>314513</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>FILEZINHO DE PEITO DE FRANGO SEARA 1KG</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="n">
+      <c r="C14" s="8" t="n">
+        <v>157014</v>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO COM OSSO KG</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>105470</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="10" t="n">
         <v>23.99</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 04 E 05/02/26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>292399</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="n">
-        <v>10.99</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 04 E 05/02/26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>301962</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>LINGUIÇA SUÍNA BONFRIGO KG</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="n">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>106283</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ALMONDEGA KG TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
         <v>16.99</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>152232</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>BUCHO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="10" t="n">
+        <v>12.99</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>104905</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>BANANA NANICA KG</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="6" t="n">
-        <v>5.99</v>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>COSTELA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="10" t="n">
+        <v>18.99</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>105023</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="n">
-        <v>5.99</v>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>105449</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>COXÃO DURO KG</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="10" t="n">
+        <v>34.99</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>104931</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>LARANJA KG</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="n">
-        <v>6.99</v>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>105435</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>COXÃO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="10" t="n">
+        <v>38.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 04 E 05/02/26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>104855</v>
+        <v>314513</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>LIMÃO TAITI KG</t>
+          <t>FILEZINHO DE PEITO DE FRANGO SEARA 1KG</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="6" t="n">
-        <v>6.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>104928</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG PALMER</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="n">
-        <v>6.99</v>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>173342</v>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>MOCOTO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="10" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>104883</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG TOMY</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="n">
-        <v>6.99</v>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>258810</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>PANCETA SUINA KG</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="10" t="n">
+        <v>16.99</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>104944</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>MAÇÃ NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="6" t="n">
-        <v>14.99</v>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>106032</v>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>TOUCINHO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="10" t="n">
+        <v>16.99</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>104947</v>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="n">
-        <v>2.39</v>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 04/02/26</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>LINGUIÇA CASEIRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="10" t="n">
+        <v>16.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 04 E 05/02/26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>104996</v>
+        <v>292399</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>MELÃO AMARELO KG</t>
+          <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="6" t="n">
-        <v>6.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>QUARTA - HORTIFRUTI</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 04 E 05/02/26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>104903</v>
+        <v>301962</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>BATATA DOCE KG ROSA</t>
+          <t>LINGUIÇA SUÍNA BONFRIGO KG</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="6" t="n">
-        <v>6.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>105010</v>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="n">
-        <v>3.99</v>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1147,20 +1183,20 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>105001</v>
+        <v>104905</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>BANANA NANICA KG</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="6" t="n">
-        <v>4.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="30">
@@ -1171,20 +1207,20 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>104862</v>
+        <v>105023</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="6" t="n">
-        <v>4.39</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="31">
@@ -1195,20 +1231,20 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>104961</v>
+        <v>104931</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="32">
@@ -1219,20 +1255,20 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>104937</v>
+        <v>104855</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>ALHO A GRANEL KG</t>
+          <t>LIMÃO TAITI KG</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="n">
-        <v>24.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="33">
@@ -1243,20 +1279,20 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>104919</v>
+        <v>104928</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
+          <t>MANGA KG PALMER</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="n">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="34">
@@ -1267,29 +1303,45 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>104992</v>
+        <v>104883</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>MANGA KG TOMY</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="n">
-        <v>2.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>104944</v>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>MAÇÃ NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="6" t="n">
+        <v>14.99</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1299,24 +1351,20 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>#10 OVOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>331438</v>
+        <v>104947</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>OVOS DE GRANJA IANA BDJ 20UN</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>BRANCOS</t>
-        </is>
-      </c>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="6" t="n">
-        <v>11.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="37">
@@ -1327,19 +1375,271 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>#10 OVOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>328966</v>
+        <v>104996</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
+          <t>MELÃO AMARELO KG</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="6" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>104903</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>BATATA DOCE KG ROSA</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="6" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>105010</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="10" t="n">
+        <v>4.89</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>105001</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="6" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>104862</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="10" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>104961</v>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="10" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>104937</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>ALHO A GRANEL KG</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="10" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>104919</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>CEBOLA NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>104992</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="6" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>#10 OVOS</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>331438</v>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>OVOS DE GRANJA IANA BDJ 20UN</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>BRANCOS</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>#10 OVOS</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>328966</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="6" t="n">
         <v>17.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998BAFA7-EECC-4EDB-9F48-9AE69E8B6CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AA5776-D940-42E0-A0AE-742186D4849B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -229,7 +224,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,21 +244,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -307,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -315,22 +320,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,843 +646,843 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="67.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>100038</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>322738</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>258150</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>302944</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>147352</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>20.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>320121</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>291441</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>105470</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>239334</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>105457</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>105463</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>105449</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>314513</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>24.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>105474</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>105062</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>106008</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>106052</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>106050</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>9.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>189031</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>292399</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>11.49</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>301962</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>340725</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>325449</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>169242</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>173481</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="7"/>
+      <c r="F28" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>338955</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="7"/>
+      <c r="F29" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>104905</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="7"/>
+      <c r="F31" s="8">
         <v>5.49</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>105023</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="7"/>
+      <c r="F32" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>104931</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="E33" s="7"/>
+      <c r="F33" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>104855</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="E34" s="7"/>
+      <c r="F34" s="8">
         <v>3.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>104881</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
+      <c r="E35" s="7"/>
+      <c r="F35" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>104928</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
+      <c r="E36" s="7"/>
+      <c r="F36" s="8">
         <v>6.49</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>104883</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
+      <c r="E37" s="7"/>
+      <c r="F37" s="8">
         <v>6.49</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>108982</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
+      <c r="E38" s="7"/>
+      <c r="F38" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>104944</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
+      <c r="E39" s="7"/>
+      <c r="F39" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>104947</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
+      <c r="E40" s="7"/>
+      <c r="F40" s="8">
         <v>2.19</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>104996</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7">
+      <c r="E41" s="7"/>
+      <c r="F41" s="8">
         <v>6.49</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="5">
         <v>104903</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7">
+      <c r="E42" s="7"/>
+      <c r="F42" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="5">
         <v>105010</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="7">
+      <c r="E43" s="7"/>
+      <c r="F43" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="5">
         <v>105001</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="7">
+      <c r="E44" s="7"/>
+      <c r="F44" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="5">
         <v>104862</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7">
+      <c r="E45" s="7"/>
+      <c r="F45" s="8">
         <v>3.99</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="5">
         <v>104961</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7">
+      <c r="E46" s="7"/>
+      <c r="F46" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="5">
         <v>104937</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
+      <c r="E47" s="7"/>
+      <c r="F47" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="5">
         <v>104919</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="7">
+      <c r="E48" s="7"/>
+      <c r="F48" s="8">
         <v>2.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="5">
         <v>104992</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="7">
+      <c r="E49" s="7"/>
+      <c r="F49" s="8">
         <v>2.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -1,40 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D1B4B6-89BC-4801-AAB9-CBA02447D20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81681F94-A2B5-460A-8C4B-B637467E3DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="174">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -285,6 +271,9 @@
     <t>DETERGENTE LIQUIDO YPÊ 500ML</t>
   </si>
   <si>
+    <t>CAPIM LIMÃO, CLEAR, CLEAR CARE, COCO, LIMAO, MACA, NEUTRO</t>
+  </si>
+  <si>
     <t>#03 LIMPEZA - LAVA ROUPAS</t>
   </si>
   <si>
@@ -307,6 +296,9 @@
   </si>
   <si>
     <t>ODORIZADOR DE AR LADY PRIME 360ML</t>
+  </si>
+  <si>
+    <t>LAVANDA, ORVALHO DO CAMPO, TOQUE DE PRIMAVERA</t>
   </si>
   <si>
     <t>#03 LIMPEZA - SABÃO</t>
@@ -557,9 +549,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,8 +587,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,6 +617,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -637,7 +653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -654,13 +670,21 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,21 +987,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:F121"/>
-  <sheetFormatPr defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -993,11 +1014,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1011,11 +1032,11 @@
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>21.49</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1029,11 +1050,11 @@
         <v>9</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1047,11 +1068,11 @@
         <v>10</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>22.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1065,11 +1086,11 @@
         <v>11</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1083,11 +1104,11 @@
         <v>13</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>6.49</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1101,11 +1122,11 @@
         <v>15</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>8.19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -1119,11 +1140,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>8.19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -1137,11 +1158,11 @@
         <v>19</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>32.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -1155,11 +1176,11 @@
         <v>21</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>15.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -1173,11 +1194,11 @@
         <v>22</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>14.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1191,11 +1212,11 @@
         <v>24</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>7.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -1209,11 +1230,11 @@
         <v>25</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -1227,11 +1248,11 @@
         <v>27</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -1245,11 +1266,11 @@
         <v>28</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>9.49</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1263,11 +1284,11 @@
         <v>29</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>99.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -1281,11 +1302,11 @@
         <v>30</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>6.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -1299,11 +1320,11 @@
         <v>31</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>3.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -1317,11 +1338,11 @@
         <v>32</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <v>13.59</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
@@ -1337,11 +1358,11 @@
       <c r="E21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <v>13.49</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1357,11 +1378,11 @@
       <c r="E22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>37</v>
       </c>
@@ -1375,11 +1396,11 @@
         <v>39</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <v>10.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1393,11 +1414,11 @@
         <v>41</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="F24" s="6">
         <v>5.89</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
@@ -1411,11 +1432,11 @@
         <v>42</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <v>4.79</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
@@ -1429,11 +1450,11 @@
         <v>43</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <v>23.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -1449,11 +1470,11 @@
       <c r="E27" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>11.69</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -1467,11 +1488,11 @@
         <v>48</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="F28" s="6">
         <v>2.69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
@@ -1485,11 +1506,11 @@
         <v>49</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="F29" s="6">
         <v>6.49</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
@@ -1503,11 +1524,11 @@
         <v>50</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="F30" s="6">
         <v>7.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
@@ -1521,11 +1542,11 @@
         <v>51</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="F31" s="6">
         <v>2.19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
@@ -1539,11 +1560,11 @@
         <v>52</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="F32" s="6">
         <v>1.59</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
@@ -1557,11 +1578,11 @@
         <v>53</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="F33" s="6">
         <v>7.69</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
@@ -1575,11 +1596,11 @@
         <v>54</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="F34" s="6">
         <v>7.39</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
@@ -1593,11 +1614,11 @@
         <v>56</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="7">
+      <c r="F35" s="6">
         <v>13.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>37</v>
       </c>
@@ -1611,11 +1632,11 @@
         <v>58</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="7">
+      <c r="F36" s="6">
         <v>8.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
@@ -1629,11 +1650,11 @@
         <v>59</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="7">
+      <c r="F37" s="6">
         <v>7.19</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
@@ -1647,11 +1668,11 @@
         <v>61</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="7">
+      <c r="F38" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1665,11 +1686,11 @@
         <v>62</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="7">
+      <c r="F39" s="6">
         <v>8.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
@@ -1683,11 +1704,11 @@
         <v>64</v>
       </c>
       <c r="E40" s="5"/>
-      <c r="F40" s="7">
+      <c r="F40" s="6">
         <v>39.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
@@ -1701,11 +1722,11 @@
         <v>65</v>
       </c>
       <c r="E41" s="5"/>
-      <c r="F41" s="7">
+      <c r="F41" s="6">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>37</v>
       </c>
@@ -1719,11 +1740,11 @@
         <v>67</v>
       </c>
       <c r="E42" s="5"/>
-      <c r="F42" s="7">
+      <c r="F42" s="6">
         <v>6.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>37</v>
       </c>
@@ -1737,11 +1758,11 @@
         <v>68</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="7">
+      <c r="F43" s="6">
         <v>10.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>37</v>
       </c>
@@ -1755,11 +1776,11 @@
         <v>69</v>
       </c>
       <c r="E44" s="5"/>
-      <c r="F44" s="7">
+      <c r="F44" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
@@ -1773,11 +1794,11 @@
         <v>71</v>
       </c>
       <c r="E45" s="5"/>
-      <c r="F45" s="7">
+      <c r="F45" s="6">
         <v>2.99</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
@@ -1791,11 +1812,11 @@
         <v>72</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="7">
+      <c r="F46" s="6">
         <v>3.19</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
@@ -1809,11 +1830,11 @@
         <v>73</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="7">
+      <c r="F47" s="6">
         <v>2.79</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
@@ -1827,11 +1848,11 @@
         <v>75</v>
       </c>
       <c r="E49" s="5"/>
-      <c r="F49" s="7">
+      <c r="F49" s="6">
         <v>7.19</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
@@ -1845,11 +1866,11 @@
         <v>77</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="7">
+      <c r="F50" s="6">
         <v>7.99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -1863,11 +1884,11 @@
         <v>78</v>
       </c>
       <c r="E51" s="5"/>
-      <c r="F51" s="7">
+      <c r="F51" s="6">
         <v>33.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
@@ -1881,11 +1902,11 @@
         <v>80</v>
       </c>
       <c r="E52" s="5"/>
-      <c r="F52" s="7">
+      <c r="F52" s="6">
         <v>15.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
@@ -1898,1178 +1919,1176 @@
       <c r="D53" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="7">
+      <c r="E53" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F53" s="6">
         <v>2.89</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C54" s="3">
         <v>297206</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F54" s="7">
+        <v>86</v>
+      </c>
+      <c r="F54" s="6">
         <v>11.39</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C55" s="3">
         <v>100511</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F55" s="7">
+        <v>89</v>
+      </c>
+      <c r="F55" s="6">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C56" s="3">
         <v>321018</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="7">
+        <v>91</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F56" s="6">
         <v>15.99</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C57" s="3">
         <v>261360</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E57" s="5"/>
-      <c r="F57" s="7">
+      <c r="F57" s="6">
         <v>9.99</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C58" s="3">
         <v>263649</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="7">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="C59" s="3">
         <v>259568</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F59" s="7">
+        <v>86</v>
+      </c>
+      <c r="F59" s="6">
         <v>10.49</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C60" s="3">
         <v>100373</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E60" s="5"/>
-      <c r="F60" s="7">
+      <c r="F60" s="6">
         <v>24.99</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C62" s="3">
         <v>104406</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="7">
+      <c r="F62" s="6">
         <v>10.39</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C63" s="3">
         <v>104404</v>
       </c>
       <c r="D63" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="7">
-        <v>9.49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="C64" s="3">
         <v>104424</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E64" s="5"/>
-      <c r="F64" s="7">
+      <c r="F64" s="6">
         <v>6.99</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C65" s="3">
         <v>117100</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E65" s="5"/>
-      <c r="F65" s="7">
+      <c r="F65" s="6">
         <v>13.99</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C66" s="3">
         <v>102285</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E66" s="5"/>
-      <c r="F66" s="7">
+      <c r="F66" s="6">
         <v>6.99</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C67" s="3">
         <v>132194</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E67" s="5"/>
-      <c r="F67" s="7">
+      <c r="F67" s="6">
         <v>19.39</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C68" s="3">
         <v>338379</v>
       </c>
       <c r="D68" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="6">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="E68" s="5"/>
-      <c r="F68" s="7">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C69" s="3">
         <v>322794</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E69" s="5"/>
-      <c r="F69" s="7">
+      <c r="F69" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C70" s="3">
         <v>327173</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E70" s="5"/>
-      <c r="F70" s="7">
+      <c r="F70" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C71" s="3">
         <v>102149</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E71" s="5"/>
-      <c r="F71" s="7">
+      <c r="F71" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C72" s="3">
         <v>239441</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E72" s="5"/>
-      <c r="F72" s="7">
+      <c r="F72" s="6">
         <v>3.09</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C73" s="3">
         <v>184034</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E73" s="5"/>
-      <c r="F73" s="7">
+      <c r="F73" s="6">
         <v>4.99</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C74" s="3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" s="8">
         <v>313599</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E74" s="5"/>
-      <c r="F74" s="7">
-        <f>15*3.59</f>
-        <v>53.849999999999994</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C75" s="3">
+      <c r="D74" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E74" s="9"/>
+      <c r="F74" s="10">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C75" s="8">
         <v>324556</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E75" s="5"/>
-      <c r="F75" s="7">
-        <f>15*2.89</f>
-        <v>43.35</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D75" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="10">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C76" s="3">
         <v>102242</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E76" s="5"/>
-      <c r="F76" s="7">
+      <c r="F76" s="6">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C77" s="3">
         <v>102075</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E77" s="5"/>
-      <c r="F77" s="7">
+      <c r="F77" s="6">
         <v>129.99</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C79" s="3">
         <v>289785</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E79" s="5"/>
-      <c r="F79" s="7">
+      <c r="F79" s="6">
         <v>12.99</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C80" s="3">
         <v>325998</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E80" s="5"/>
-      <c r="F80" s="7">
+      <c r="F80" s="6">
         <v>31.99</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C81" s="3">
         <v>289795</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E81" s="5"/>
-      <c r="F81" s="7">
+      <c r="F81" s="6">
         <v>14.99</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C82" s="3">
         <v>119927</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E82" s="5"/>
-      <c r="F82" s="7">
+      <c r="F82" s="6">
         <v>10.99</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C83" s="3">
         <v>320121</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E83" s="5"/>
-      <c r="F83" s="7">
+      <c r="F83" s="6">
         <v>23.99</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C84" s="3">
         <v>195365</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E84" s="5"/>
-      <c r="F84" s="7">
+      <c r="F84" s="6">
         <v>15.99</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C85" s="3">
         <v>291441</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E85" s="5"/>
-      <c r="F85" s="7">
+      <c r="F85" s="6">
         <v>14.99</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C86" s="3">
         <v>105461</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E86" s="5"/>
-      <c r="F86" s="7">
+      <c r="F86" s="6">
         <v>34.99</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C87" s="3">
         <v>239334</v>
       </c>
       <c r="D87" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E87" s="5"/>
+      <c r="F87" s="6">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="E87" s="5"/>
-      <c r="F87" s="7">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C88" s="3">
         <v>105458</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E88" s="5"/>
-      <c r="F88" s="7">
+      <c r="F88" s="6">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C89" s="3">
         <v>105463</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E89" s="5"/>
-      <c r="F89" s="7">
+      <c r="F89" s="6">
         <v>13.99</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C90" s="3">
         <v>105449</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E90" s="5"/>
-      <c r="F90" s="7">
+      <c r="F90" s="6">
         <v>34.99</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C91" s="3">
         <v>105435</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E91" s="5"/>
-      <c r="F91" s="7">
+      <c r="F91" s="6">
         <v>38.99</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C92" s="3">
         <v>106053</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E92" s="5"/>
-      <c r="F92" s="7">
+      <c r="F92" s="6">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C93" s="3">
         <v>105433</v>
       </c>
       <c r="D93" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E93" s="5"/>
+      <c r="F93" s="6">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="E93" s="5"/>
-      <c r="F93" s="7">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="C94" s="3">
         <v>258810</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E94" s="5"/>
-      <c r="F94" s="7">
+      <c r="F94" s="6">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C95" s="3">
         <v>106050</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E95" s="5"/>
-      <c r="F95" s="7">
+      <c r="F95" s="6">
         <v>9.99</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C96" s="3">
         <v>305039</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E96" s="5"/>
-      <c r="F96" s="7">
+      <c r="F96" s="6">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C97" s="3">
         <v>289127</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E97" s="5"/>
-      <c r="F97" s="7">
+      <c r="F97" s="6">
         <v>7.99</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C98" s="3">
         <v>189031</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E98" s="5"/>
-      <c r="F98" s="7">
+      <c r="F98" s="6">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C100" s="3">
         <v>104998</v>
       </c>
       <c r="D100" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E100" s="5"/>
+      <c r="F100" s="6">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E100" s="5"/>
-      <c r="F100" s="7">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="B101" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C101" s="3">
         <v>104905</v>
       </c>
       <c r="D101" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E101" s="5"/>
+      <c r="F101" s="6">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="E101" s="5"/>
-      <c r="F101" s="7">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="C102" s="3">
         <v>105023</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E102" s="5"/>
-      <c r="F102" s="7">
+      <c r="F102" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C103" s="3">
         <v>104931</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E103" s="5"/>
-      <c r="F103" s="7">
+      <c r="F103" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C104" s="3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C104" s="8">
         <v>104855</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E104" s="5"/>
-      <c r="F104" s="7">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D104" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E104" s="9"/>
+      <c r="F104" s="10">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C105" s="3">
         <v>104881</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E105" s="5"/>
-      <c r="F105" s="7">
+      <c r="F105" s="6">
         <v>6.99</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C106" s="3">
         <v>104928</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E106" s="5"/>
-      <c r="F106" s="7">
+      <c r="F106" s="6">
         <v>6.99</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C107" s="3">
         <v>104944</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E107" s="5"/>
-      <c r="F107" s="7">
+      <c r="F107" s="6">
         <v>13.99</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C108" s="3">
         <v>104947</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E108" s="5"/>
-      <c r="F108" s="7">
+      <c r="F108" s="6">
         <v>2.19</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C109" s="3">
         <v>104996</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E109" s="5"/>
-      <c r="F109" s="7">
+      <c r="F109" s="6">
         <v>7.99</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C110" s="3">
         <v>113290</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E110" s="5"/>
-      <c r="F110" s="7">
+      <c r="F110" s="6">
         <v>13.99</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C111" s="3">
         <v>104903</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E111" s="5"/>
-      <c r="F111" s="7">
+      <c r="F111" s="6">
         <v>6.99</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C112" s="3">
         <v>105010</v>
       </c>
       <c r="D112" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E112" s="5"/>
+      <c r="F112" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="E112" s="5"/>
-      <c r="F112" s="7">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="C113" s="3">
         <v>105001</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E113" s="5"/>
-      <c r="F113" s="7">
+      <c r="F113" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C114" s="3">
         <v>104862</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E114" s="5"/>
-      <c r="F114" s="7">
+      <c r="F114" s="6">
         <v>5.99</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C115" s="3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C115" s="8">
         <v>104961</v>
       </c>
-      <c r="D115" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E115" s="5"/>
-      <c r="F115" s="7">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D115" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E115" s="9"/>
+      <c r="F115" s="10">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C116" s="3">
         <v>104937</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E116" s="5"/>
-      <c r="F116" s="7">
+      <c r="F116" s="6">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C117" s="3">
         <v>104919</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E117" s="5"/>
-      <c r="F117" s="7">
+      <c r="F117" s="6">
         <v>2.99</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C118" s="3">
         <v>104992</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E118" s="5"/>
-      <c r="F118" s="7">
+      <c r="F118" s="6">
         <v>2.99</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C120" s="3">
         <v>331438</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E120" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F120" s="6">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="F120" s="7">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="C121" s="3">
         <v>328966</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E121" s="5"/>
-      <c r="F121" s="7">
+      <c r="F121" s="6">
         <v>17.989999999999998</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="84" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - QUARTA&amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C53825-9004-4483-AD2A-A5F66F5C0AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7AABEA-EB79-4D23-A5DC-AA6E43D4DC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,6 +585,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1211,6 +1214,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - QUARTA&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A5A7DB-A504-4364-A3A2-7D1721BF8A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ECF07A-8FD5-4CD9-9164-8DBD1182B895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -239,9 +234,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,24 +256,47 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,6 +307,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -327,22 +351,34 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,885 +685,885 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>100038</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>276943</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>287263</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>306945</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>228068</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>238317</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>7.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>228090</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>104770</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>7.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>111324</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>20.49</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>108785</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>108786</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>109388</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>225767</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>302029</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>105470</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>239334</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>29.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>105457</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>322584</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>38.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>105468</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>105471</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>107260</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
         <v>32.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>105433</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>106054</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>20.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>106050</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
         <v>9.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>106034</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="7"/>
+      <c r="F28" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>304309</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="7"/>
+      <c r="F29" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>305039</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="7"/>
+      <c r="F30" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>146797</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="7"/>
+      <c r="F31" s="8">
         <v>27.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>146785</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="7"/>
+      <c r="F32" s="8">
         <v>27.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>104998</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="E34" s="7"/>
+      <c r="F34" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>104905</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
+      <c r="E35" s="7"/>
+      <c r="F35" s="8">
         <v>5.49</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>105023</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
+      <c r="E36" s="7"/>
+      <c r="F36" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="10">
         <v>104931</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E37" s="11"/>
+      <c r="F37" s="12">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>104855</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
+      <c r="E38" s="7"/>
+      <c r="F38" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>104928</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
+      <c r="E39" s="7"/>
+      <c r="F39" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>104883</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
+      <c r="E40" s="7"/>
+      <c r="F40" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="10">
         <v>104944</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E41" s="11"/>
+      <c r="F41" s="12">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="5">
         <v>104947</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7">
+      <c r="E42" s="7"/>
+      <c r="F42" s="8">
         <v>2.39</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="5">
         <v>104996</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="7">
+      <c r="E43" s="7"/>
+      <c r="F43" s="8">
         <v>7.69</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="5">
         <v>113290</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="7">
+      <c r="E44" s="7"/>
+      <c r="F44" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="5">
         <v>105010</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7">
+      <c r="E45" s="7"/>
+      <c r="F45" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="10">
         <v>105001</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E46" s="11"/>
+      <c r="F46" s="12">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="5">
         <v>104862</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
+      <c r="E47" s="7"/>
+      <c r="F47" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="10">
         <v>104961</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="7">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E48" s="11"/>
+      <c r="F48" s="12">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="5">
         <v>104937</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="7">
+      <c r="E49" s="7"/>
+      <c r="F49" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="10">
         <v>104919</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="7">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E50" s="11"/>
+      <c r="F50" s="12">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="5">
         <v>104992</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="7">
+      <c r="E51" s="7"/>
+      <c r="F51" s="8">
         <v>5.69</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - QUARTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - QUARTA.xlsx
+++ b/giro_da_praça_ofertas - QUARTA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3CAAC8-3F71-45BC-A7D4-B34CB2BB57A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42382ED4-490F-408E-B335-EBD95E5A975D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -226,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,21 +241,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -304,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -312,22 +317,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,807 +643,807 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="36.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="62.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>100038</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>312226</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>26.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>127336</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>246975</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>206159</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>109759</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>146742</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>20.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>289785</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>147352</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>108770</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>225767</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>298984</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>289794</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>24.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>291441</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>105470</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>239334</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>105456</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>29.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>105468</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>105435</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>38.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>107260</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>32.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>106053</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>106034</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>106032</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>304309</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>305039</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="7"/>
+      <c r="F28" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>104998</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="7"/>
+      <c r="F30" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>104905</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="7"/>
+      <c r="F31" s="8">
         <v>5.49</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>105023</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="7"/>
+      <c r="F32" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>104931</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="E33" s="7"/>
+      <c r="F33" s="8">
         <v>6.59</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>104855</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="E34" s="7"/>
+      <c r="F34" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>104928</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
+      <c r="E35" s="7"/>
+      <c r="F35" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>104883</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
+      <c r="E36" s="7"/>
+      <c r="F36" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>104944</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
+      <c r="E37" s="7"/>
+      <c r="F37" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>104947</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
+      <c r="E38" s="7"/>
+      <c r="F38" s="8">
         <v>2.39</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>104996</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
+      <c r="E39" s="7"/>
+      <c r="F39" s="8">
         <v>7.69</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>113290</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
+      <c r="E40" s="7"/>
+      <c r="F40" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>105010</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7">
+      <c r="E41" s="7"/>
+      <c r="F41" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="5">
         <v>105001</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7">
+      <c r="E42" s="7"/>
+      <c r="F42" s="8">
         <v>6.39</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="5">
         <v>104862</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="7">
+      <c r="E43" s="7"/>
+      <c r="F43" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="5">
         <v>104961</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="7">
+      <c r="E44" s="7"/>
+      <c r="F44" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="5">
         <v>104937</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7">
+      <c r="E45" s="7"/>
+      <c r="F45" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="5">
         <v>104919</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7">
+      <c r="E46" s="7"/>
+      <c r="F46" s="8">
         <v>3.89</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="5">
         <v>104992</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
+      <c r="E47" s="7"/>
+      <c r="F47" s="8">
         <v>5.69</v>
       </c>
     </row>
